--- a/other/Attributenkonzept_Quellen.xlsx
+++ b/other/Attributenkonzept_Quellen.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" state="visible" r:id="rId3"/>
@@ -1356,9 +1356,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>821520</xdr:colOff>
+      <xdr:colOff>821160</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>32400</xdr:rowOff>
+      <xdr:rowOff>32040</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1368,7 +1368,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1517400" y="2685960"/>
-          <a:ext cx="2593440" cy="2659320"/>
+          <a:ext cx="2593080" cy="2658960"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -1445,9 +1445,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>570600</xdr:colOff>
+      <xdr:colOff>570240</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>161280</xdr:rowOff>
+      <xdr:rowOff>160920</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1457,7 +1457,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="869760" y="1906200"/>
-          <a:ext cx="1345320" cy="1396440"/>
+          <a:ext cx="1344960" cy="1396080"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -1526,9 +1526,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>161280</xdr:colOff>
+      <xdr:colOff>160920</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>125640</xdr:rowOff>
+      <xdr:rowOff>125280</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1538,7 +1538,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2867040" y="2200320"/>
-          <a:ext cx="1405800" cy="1428480"/>
+          <a:ext cx="1405440" cy="1428120"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -1644,9 +1644,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>217800</xdr:colOff>
+      <xdr:colOff>217440</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>114840</xdr:rowOff>
+      <xdr:rowOff>114480</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1656,7 +1656,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1702440" y="3428640"/>
-          <a:ext cx="1804680" cy="1818360"/>
+          <a:ext cx="1804320" cy="1818000"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -1724,9 +1724,9 @@
   <xdr:twoCellAnchor editAs="twoCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>172080</xdr:colOff>
+      <xdr:colOff>172440</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>67320</xdr:rowOff>
+      <xdr:rowOff>67680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
@@ -1741,8 +1741,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm rot="10800000">
-          <a:off x="6971040" y="2515320"/>
-          <a:ext cx="1532880" cy="1142280"/>
+          <a:off x="6971400" y="2515680"/>
+          <a:ext cx="1532520" cy="1141920"/>
         </a:xfrm>
         <a:prstGeom prst="stripedRightArrow">
           <a:avLst>
@@ -1786,9 +1786,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>46800</xdr:colOff>
+      <xdr:colOff>46440</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>84600</xdr:rowOff>
+      <xdr:rowOff>84240</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1798,7 +1798,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="8646840" y="3981240"/>
-          <a:ext cx="145080" cy="542160"/>
+          <a:ext cx="144720" cy="541800"/>
         </a:xfrm>
         <a:prstGeom prst="leftBrace">
           <a:avLst>
@@ -1838,9 +1838,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>16560</xdr:colOff>
+      <xdr:colOff>16200</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>46800</xdr:rowOff>
+      <xdr:rowOff>46440</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1850,7 +1850,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="8685000" y="1571760"/>
-          <a:ext cx="76680" cy="199080"/>
+          <a:ext cx="76320" cy="198720"/>
         </a:xfrm>
         <a:prstGeom prst="leftBrace">
           <a:avLst>
